--- a/output/pdf_financials_xlsx/AVCR.xlsx
+++ b/output/pdf_financials_xlsx/AVCR.xlsx
@@ -5924,10 +5924,10 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.64496</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.678819</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>2.017741</v>
@@ -5939,28 +5939,28 @@
         <v>3.952879</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.275882</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.119838</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.358462</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.794718</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.933708</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.558433</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.067518</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>7.348195</v>
       </c>
     </row>
     <row r="93">
@@ -9810,7 +9810,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10707,7 +10711,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -12489,7 +12497,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -13598,7 +13610,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -15939,7 +15955,11 @@
           <t>Prepaids and deposits (Note 5)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -17125,7 +17145,11 @@
           <t>Reserves (Notes 11 and 19)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -18428,7 +18452,11 @@
           <t>Reserves (Notes 11)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -35715,7 +35743,11 @@
           <t>Prepaid and deposit</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AVCR.xlsx
+++ b/output/pdf_financials_xlsx/AVCR.xlsx
@@ -930,16 +930,16 @@
         <v>3.476057</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.002996</v>
+        <v>2.178161</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.114996</v>
+        <v>0.504923</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.147157</v>
+        <v>0.193095</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.395349</v>
+        <v>0.774633</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.732986</v>
@@ -988,7 +988,7 @@
         <v>-3.26681</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.302596</v>
+        <v>-1.872569</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-0.421562</v>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.03874</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.076181</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.069886</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1058,34 +1058,34 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000126</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.00848</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.001715</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000405</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000581</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.008085999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.003284</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.001235</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.012124</v>
       </c>
     </row>
     <row r="13">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.937735</v>
+        <v>-1.976475</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.183009</v>
+        <v>-1.25919</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.992659</v>
+        <v>-4.062545</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.875565</v>
@@ -2022,34 +2022,34 @@
         <v>-0.733946</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.200648</v>
+        <v>-2.200774</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.613904</v>
+        <v>-2.622384</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-2.736717</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.136802</v>
+        <v>-4.138517</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.105608</v>
+        <v>-2.106013</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.708132</v>
+        <v>-1.708713</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.818228</v>
+        <v>-0.826314</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.701215</v>
+        <v>-0.704499</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.668977</v>
+        <v>-0.670212</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.858747</v>
+        <v>-1.870871</v>
       </c>
     </row>
     <row r="28">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.937735</v>
+        <v>-1.976475</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.183009</v>
+        <v>-1.25919</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.992659</v>
+        <v>-4.062545</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.875565</v>
@@ -2138,34 +2138,34 @@
         <v>-0.733946</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.200648</v>
+        <v>-2.200774</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.613904</v>
+        <v>-2.622384</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-2.736717</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.136802</v>
+        <v>-4.138517</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.105608</v>
+        <v>-2.106013</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.708132</v>
+        <v>-1.708713</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.818228</v>
+        <v>-0.826314</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.701215</v>
+        <v>-0.704499</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.668977</v>
+        <v>-0.670212</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.858747</v>
+        <v>-1.870871</v>
       </c>
     </row>
     <row r="30">
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-778.0755856441885</v>
+        <v>-793.6311947382369</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-419.1188297355994</v>
+        <v>-446.1083890441826</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-273.5286219090955</v>
+        <v>-278.3163639303247</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-613.7480693211864</v>
@@ -2200,34 +2200,34 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-38520.00700157536</v>
+        <v>-38522.212497812</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-106.1728324856932</v>
+        <v>-106.5172772776513</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>-169.2378808014184</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-27046.76037920889</v>
+        <v>-27057.9731938542</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-6380.630303030302</v>
+        <v>-6381.857575757575</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-1390.896358543417</v>
+        <v>-1391.369454758648</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-46.27007635262677</v>
+        <v>-46.72733256652722</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-20.12009823401997</v>
+        <v>-20.21432668406813</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-13.97863347786776</v>
+        <v>-14.00443946573456</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-348.1555918514134</v>
+        <v>-350.4264971417012</v>
       </c>
     </row>
     <row r="31">
@@ -7778,7 +7778,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.052007</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -7836,7 +7836,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.052007</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -27503,7 +27503,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -45036,7 +45040,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -58549,7 +58553,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -63017,7 +63021,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -64942,7 +64946,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -68754,7 +68758,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E603" s="5" t="n">

--- a/output/pdf_financials_xlsx/AVCR.xlsx
+++ b/output/pdf_financials_xlsx/AVCR.xlsx
@@ -1599,10 +1599,10 @@
         <v>-2.736717</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-4.136802</v>
+        <v>-3.458141</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-2.105608</v>
+        <v>-1.916252</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-1.708132</v>
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-0.678661</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>-0.189356</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>0</v>
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.001428</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.012199</v>
       </c>
     </row>
     <row r="41">
@@ -2804,7 +2804,7 @@
         <v>0.011695</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.015629</v>
+        <v>0.017057</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0.113198</v>
@@ -2834,7 +2834,7 @@
         <v>0.419587</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>0.037332</v>
+        <v>0.049531</v>
       </c>
     </row>
     <row r="42">
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.001072</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.063897</v>
@@ -3254,7 +3254,7 @@
         <v>0.03047</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.101083</v>
+        <v>0.088884</v>
       </c>
     </row>
     <row r="49">
@@ -4214,43 +4214,43 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.330986</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.199785</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.110343</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.111166</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.100342</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.160249</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.226575</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.62546</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.044477</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.261493</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.428677</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.255965</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.172521</v>
       </c>
     </row>
     <row r="65">
@@ -4400,22 +4400,22 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.135064</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.14184</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.08766400000000001</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="N67" s="3" t="n">
         <v>0</v>
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.02139</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.02139</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>0.04</v>
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.02139</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>0</v>
@@ -5214,10 +5214,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>-0.04595542817611306</v>
       </c>
       <c r="N80" s="3" t="n">
         <v>0.01820734156426554</v>
@@ -6313,10 +6311,10 @@
         <v>-2.736717</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>-4.136802</v>
+        <v>-3.458141</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>-2.105608</v>
+        <v>-1.916252</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>-1.708132</v>
@@ -7003,31 +7001,31 @@
         <v>-0.030846</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00634</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003784</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.105358</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-1.193345</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-1.021571</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.181094</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.08849700000000001</v>
       </c>
     </row>
     <row r="112">
@@ -8391,31 +8389,31 @@
         <v>-0.030846</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00634</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003784</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.105358</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-1.193345</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-1.021571</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.181094</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.08849700000000001</v>
       </c>
     </row>
     <row r="135">
@@ -8461,31 +8459,31 @@
         <v>-1.515423</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-2.06409</v>
+        <v>-2.07043</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.767296</v>
+        <v>-1.77108</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-1.41089</v>
+        <v>-1.41589</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-0.862334</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-1.234154</v>
+        <v>-1.339512</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-0.437832</v>
+        <v>-1.631177</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>0.660403</v>
+        <v>-0.361168</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>1.004615</v>
+        <v>0.8235209999999999</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-0.789933</v>
+        <v>-0.87843</v>
       </c>
     </row>
   </sheetData>
@@ -12093,7 +12091,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -22630,7 +22632,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -25794,7 +25800,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -31527,7 +31537,11 @@
           <t>Proceeds from private placement -</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -33943,7 +33957,11 @@
           <t>Proceeds from private placement -</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -36054,7 +36072,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -37860,7 +37882,11 @@
           <t>Proceeds from Private Placement</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -52592,7 +52618,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
@@ -52691,7 +52721,11 @@
           <t>Loss from discontinued operations 16</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
